--- a/output/价格通知书_需商折/价格通知书_需商折.xlsx
+++ b/output/价格通知书_需商折/价格通知书_需商折.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\epsdemo\compliance_report\价格通知书_需商折\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\supply-chain-agent_in-public\output\价格通知书_需商折\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03FE8B0-117E-4B17-BF97-65B5D6A9B222}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184B1A07-D429-41C1-B1B6-4D3431714C0C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="10190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>价格通知书</t>
   </si>
@@ -35,111 +35,6 @@
   </si>
   <si>
     <t>识别日期</t>
-  </si>
-  <si>
-    <t>CJ2605260029</t>
-  </si>
-  <si>
-    <t>武汉市东亚合成汽车部件有限公司</t>
-  </si>
-  <si>
-    <t>2026年降追加商折到3.5%，追溯到2026年1月；涉及商折追回，待线下核定供货数量及商折金额后通过商折函追回。</t>
-  </si>
-  <si>
-    <t>闵守卫</t>
-  </si>
-  <si>
-    <t>CJ2605260028</t>
-  </si>
-  <si>
-    <t>十堰银轮汽车零部件有限公司</t>
-  </si>
-  <si>
-    <t>有商折追回</t>
-  </si>
-  <si>
-    <t>张锐</t>
-  </si>
-  <si>
-    <t>CJ2605250010</t>
-  </si>
-  <si>
-    <t>东方久乐汽车电子（上海）股份有限公司</t>
-  </si>
-  <si>
-    <t>1-3月预计商折追回31913.69元</t>
-  </si>
-  <si>
-    <t>胡继泽</t>
-  </si>
-  <si>
-    <t>CJ2605250007</t>
-  </si>
-  <si>
-    <t>武汉方鼎汽车部件制造有限公司</t>
-  </si>
-  <si>
-    <t>CJ2605250005</t>
-  </si>
-  <si>
-    <t>武汉雷铂汽车电器有限公司</t>
-  </si>
-  <si>
-    <t>4月预计商折追回4729.81元</t>
-  </si>
-  <si>
-    <t>CJ2605200027</t>
-  </si>
-  <si>
-    <t>广东深鹏科技股份有限公司</t>
-  </si>
-  <si>
-    <t>CJ2605190006</t>
-  </si>
-  <si>
-    <t>武汉聚鹏精密制造有限责任公司</t>
-  </si>
-  <si>
-    <t>CJ2605150012</t>
-  </si>
-  <si>
-    <t>武汉钧达汽车饰件有限公司</t>
-  </si>
-  <si>
-    <t>2026年降，X3001266颜色件，25年12月份按照2.02*856=1729.12元追商折</t>
-  </si>
-  <si>
-    <t>CJ2605140005</t>
-  </si>
-  <si>
-    <t>武汉瑞普汽车部件有限公司</t>
-  </si>
-  <si>
-    <t>CJ2605120005</t>
-  </si>
-  <si>
-    <t>武汉云鹤智博汽车零部件有限公司</t>
-  </si>
-  <si>
-    <t>CJ2605080045</t>
-  </si>
-  <si>
-    <t>武汉艾帕克汽车配件有限公司</t>
-  </si>
-  <si>
-    <t>CJ2605070014</t>
-  </si>
-  <si>
-    <t>江苏超力电器股份有限公司</t>
-  </si>
-  <si>
-    <t>1-3月预计商折追回30501.64元</t>
-  </si>
-  <si>
-    <t>CJ2605070009</t>
-  </si>
-  <si>
-    <t>湖北达峰汽车智能控制系统有限公司</t>
   </si>
 </sst>
 </file>
@@ -547,225 +442,43 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="4">
-        <v>46171</v>
-      </c>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4">
-        <v>46171</v>
-      </c>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4">
-        <v>46171</v>
-      </c>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="4">
-        <v>46171</v>
-      </c>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="4">
-        <v>46171</v>
-      </c>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="4">
-        <v>46171</v>
-      </c>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="4">
-        <v>46171</v>
-      </c>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="4">
-        <v>46171</v>
-      </c>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="4">
-        <v>46171</v>
-      </c>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="4">
-        <v>46157</v>
-      </c>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="4">
-        <v>46157</v>
-      </c>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="4">
-        <v>46157</v>
-      </c>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="4">
-        <v>46157</v>
-      </c>
+      <c r="E14" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
